--- a/out/Attention-Mamba1_repeat_2_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>4.806964148813837</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.431863202161871</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>4.806964148813837</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>4.806964148813837</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.971411378658377e-05</v>
+        <v>-0.0003312041759280255</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.034271157050083</v>
+        <v>3.818294991243902</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.070141262210792</v>
+        <v>7.642492377461359</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1550935736512188</v>
+        <v>0.5725703438038631</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.344669012212989</v>
+        <v>4.964213442165141</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1939174312493386</v>
+        <v>0.7158992320964118</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.577434999204451</v>
+        <v>5.823532558920639</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2779798807365003</v>
+        <v>1.026238316803422</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.806964148813837</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.939586652200243</v>
+        <v>7.16051386063676</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2973830621331441</v>
+        <v>1.097871373854568</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.256394318062765</v>
+        <v>8.330095502679185</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3151668432754736</v>
+        <v>1.163522370061581</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.589366749386711</v>
+        <v>9.559352725407633</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1422282687904372</v>
+        <v>0.5250766713810855</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.558395874033023</v>
+        <v>9.44501533892195</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06868975306353668</v>
+        <v>0.2535873896760054</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.553435539503753</v>
+        <v>9.426703002335199</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03272862231064705</v>
+        <v>0.1208274542989809</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.550148421249739</v>
+        <v>9.414567850366323</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009695228687944207</v>
+        <v>0.03579996868743635</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.536776927799103</v>
+        <v>9.365212356316421</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006411331050210647</v>
+        <v>0.02368082476508422</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.539900545461309</v>
+        <v>9.376754617758428</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003279442181998165</v>
+        <v>0.01211831100191713</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.540043320952388</v>
+        <v>9.377295099397934</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00167511910742115</v>
+        <v>0.006197045428892576</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.540112163165668</v>
+        <v>9.377562682906634</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006262420209306106</v>
+        <v>0.002326205544923597</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.539689012578125</v>
+        <v>9.376014107204011</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003390274925168373</v>
+        <v>0.001265509204978248</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.539740542097836</v>
+        <v>9.376217689622459</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001610985596666907</v>
+        <v>0.0006069420619299129</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.539722668660461</v>
+        <v>9.376165230856573</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.73313322132442e-05</v>
+        <v>0.0003738227202124906</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.539757139649893</v>
+        <v>9.376305837537114</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.852719618924349e-05</v>
+        <v>0.0001936682473946922</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.539756848723334</v>
+        <v>9.376318146685842</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.097642140041462e-05</v>
+        <v>9.091294055537706e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.539750210546893</v>
+        <v>9.37630717964468</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.162890291091525e-05</v>
+        <v>5.639902613261016e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.53975276088553</v>
+        <v>9.376329302922722</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>3.15927894345679e-06</v>
+        <v>2.297467066328042e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.539746159571164</v>
+        <v>9.376318699030534</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>7.35242988982542e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.539740200973025</v>
+        <v>9.376310273855401</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>1.675769385467227e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.539735531704388</v>
+        <v>9.376306349408592</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.539730242556827</v>
+        <v>9.376300337982002</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.539730219822526</v>
+        <v>9.376295244739868</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.806964148813837</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.539730538102742</v>
+        <v>9.3762908797659</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1348825055873001</v>
+        <v>3.03186320216187</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.539731629349199</v>
+        <v>9.376291971012355</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.539730939742063</v>
+        <v>9.376291281405219</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.539730970054464</v>
+        <v>9.376291311717623</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.539730780601955</v>
+        <v>9.376291122265112</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.539730833648657</v>
+        <v>9.376291175311815</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.53973088669536</v>
+        <v>9.376291228358516</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.539730848804858</v>
+        <v>9.376291190468015</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.539730719977152</v>
+        <v>9.376291061640309</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.539730575993244</v>
+        <v>9.376290917656402</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.539730416853136</v>
+        <v>9.376290758516292</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.539730469899838</v>
+        <v>9.376290811562995</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.539730416853136</v>
+        <v>9.376290758516292</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.539730416853136</v>
+        <v>9.376290758516292</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.539730234978726</v>
+        <v>9.376290576641884</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.539730401696935</v>
+        <v>9.376290743360093</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.539730598727545</v>
+        <v>9.376290940390703</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.539730439587437</v>
+        <v>9.376290781250594</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.539730477477939</v>
+        <v>9.376290819141095</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.539730674508549</v>
+        <v>9.376291016171708</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.539730651774248</v>
+        <v>9.376290993437406</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.53973050021224</v>
+        <v>9.376290841875397</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.539730424431236</v>
+        <v>9.376290766094394</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.539730522946541</v>
+        <v>9.376290864609699</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.539730530524642</v>
+        <v>9.376290872187798</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.539730795758156</v>
+        <v>9.376291137421312</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.53973050021224</v>
+        <v>9.376290841875397</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.539730742711453</v>
+        <v>9.376291084374611</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.539730826070557</v>
+        <v>9.376291167733713</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.539730659352348</v>
+        <v>9.376291001015504</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.539730848804858</v>
+        <v>9.376291190468015</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.53973050021224</v>
+        <v>9.376290841875397</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.53973029560353</v>
+        <v>9.376290637266687</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.539730409275035</v>
+        <v>9.376290750938193</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.539730424431236</v>
+        <v>9.376290766094394</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.539730189510124</v>
+        <v>9.37629053117328</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.539730250134927</v>
+        <v>9.376290591798083</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.53973012130722</v>
+        <v>9.376290462970378</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.539730257713027</v>
+        <v>9.376290599376185</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.539730432009336</v>
+        <v>9.376290773672492</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.539730575993244</v>
+        <v>9.376290917656402</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.539730409275035</v>
+        <v>9.376290750938193</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.539730401696935</v>
+        <v>9.376290743360093</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.53973011372912</v>
+        <v>9.376290455392278</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.539730128885321</v>
+        <v>9.376290470548478</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.539730356228333</v>
+        <v>9.376290697891491</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.539730341072132</v>
+        <v>9.376290682735288</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.539730447165537</v>
+        <v>9.376290788828696</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.539730174353923</v>
+        <v>9.376290516017079</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.539730272869229</v>
+        <v>9.376290614532385</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.539730424431236</v>
+        <v>9.376290766094394</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.539730439587437</v>
+        <v>9.376290781250594</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.539730416853136</v>
+        <v>9.376290758516292</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.53973050021224</v>
+        <v>9.376290841875397</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.539730598727545</v>
+        <v>9.376290940390703</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.539730432009336</v>
+        <v>9.376290773672492</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.539730416853136</v>
+        <v>9.376290758516292</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.539730386540734</v>
+        <v>9.376290728203891</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.539730371384533</v>
+        <v>9.376290713047691</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.539730409275035</v>
+        <v>9.376290750938193</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.539730424431236</v>
+        <v>9.376290766094394</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.539730416853136</v>
+        <v>9.376290758516292</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.971411378658377e-05</v>
+        <v>-0.0001702487156966236</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.034271157050083</v>
+        <v>1.962716250749892</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.070141262210792</v>
+        <v>3.928466506614503</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1550935736512188</v>
+        <v>0.2943180570367409</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.344669012212989</v>
+        <v>2.551752134757981</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1939174312493386</v>
+        <v>0.3679933361985089</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.7211965688743771</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.577434999204451</v>
+        <v>2.993467489878253</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2779798807365003</v>
+        <v>0.5275167022683547</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.939586652200243</v>
+        <v>3.680715233143757</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2973830621331441</v>
+        <v>0.5643380329722558</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.256394318062765</v>
+        <v>4.281914624169513</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3151668432754736</v>
+        <v>0.5980853050984786</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.589366749386711</v>
+        <v>4.913789208780242</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1422282687904372</v>
+        <v>0.2699047745371187</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.558395874033023</v>
+        <v>4.855016446243654</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06868975306353668</v>
+        <v>0.1303510265252164</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1348825055873001</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.553435539503753</v>
+        <v>4.845603369834006</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03272862231064705</v>
+        <v>0.06210838334216721</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.550148421249739</v>
+        <v>4.839365532581605</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009695228687944207</v>
+        <v>0.01840228074926474</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.7211965688743771</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.536776927799103</v>
+        <v>4.813995053420325</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006411331050210647</v>
+        <v>0.01217112964989038</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.539900545461309</v>
+        <v>4.819926951140156</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003279442181998165</v>
+        <v>0.006227371713833546</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.540043320952388</v>
+        <v>4.820202361553724</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00167511910742115</v>
+        <v>0.003183098989336598</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.540112163165668</v>
+        <v>4.820337480361069</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006262420209306106</v>
+        <v>0.001193148823900667</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.539689012578125</v>
+        <v>4.819539021041916</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003390274925168373</v>
+        <v>0.0006484047339888131</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.539740542097836</v>
+        <v>4.819641256924198</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001610985596666907</v>
+        <v>0.000309713060421098</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.539722668660461</v>
+        <v>4.819611865148119</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.73313322132442e-05</v>
+        <v>0.000189823113252138</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.539757139649893</v>
+        <v>4.819681651151106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.852719618924349e-05</v>
+        <v>9.690754659105971e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.539756848723334</v>
+        <v>4.819685529937242</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.097642140041462e-05</v>
+        <v>4.395556340847371e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.539750210546893</v>
+        <v>4.819677469419536</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.162890291091525e-05</v>
+        <v>2.697865944406779e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.53975276088553</v>
+        <v>4.81968645009054</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>3.15927894345679e-06</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.539746159571164</v>
+        <v>4.819678591308692</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.539740200973025</v>
+        <v>4.819671810518222</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.539735531704388</v>
+        <v>4.819667389974372</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.539730242556827</v>
+        <v>4.819661811679247</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.7211965688743771</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.539730219822526</v>
+        <v>4.819656765058181</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.539730538102742</v>
+        <v>4.819657083338397</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.539731629349199</v>
+        <v>4.819658174584854</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.539730939742063</v>
+        <v>4.819657484977718</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.539730970054464</v>
+        <v>4.819657515290119</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.539730780601955</v>
+        <v>4.81965732583761</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.539730833648657</v>
+        <v>4.819657378884313</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.53973088669536</v>
+        <v>4.819657431931015</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.539730848804858</v>
+        <v>4.819657394040513</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.539730719977152</v>
+        <v>4.819657265212806</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.539730575993244</v>
+        <v>4.819657121228899</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.539730416853136</v>
+        <v>4.819656962088791</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.539730469899838</v>
+        <v>4.819657015135493</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.539730416853136</v>
+        <v>4.819656962088791</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.539730416853136</v>
+        <v>4.819656962088791</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.539730234978726</v>
+        <v>4.819656780214381</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.539730401696935</v>
+        <v>4.819656946932589</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.539730598727545</v>
+        <v>4.8196571439632</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.539730439587437</v>
+        <v>4.819656984823092</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.539730477477939</v>
+        <v>4.819657022713593</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.539730674508549</v>
+        <v>4.819657219744204</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.539730651774248</v>
+        <v>4.819657197009902</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.53973050021224</v>
+        <v>4.819657045447895</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.539730424431236</v>
+        <v>4.819656969666891</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.539730522946541</v>
+        <v>4.819657068182196</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.539730530524642</v>
+        <v>4.819657075760296</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.539730795758156</v>
+        <v>4.81965734099381</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.53973050021224</v>
+        <v>4.819657045447895</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.539730742711453</v>
+        <v>4.819657287947107</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.539730826070557</v>
+        <v>4.819657371306212</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.539730659352348</v>
+        <v>4.819657204588004</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.539730848804858</v>
+        <v>4.819657394040513</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.53973050021224</v>
+        <v>4.819657045447895</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.1382051466884343</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.53973029560353</v>
+        <v>4.819656840839184</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.539730409275035</v>
+        <v>4.819656954510689</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.539730424431236</v>
+        <v>4.819656969666891</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.539730189510124</v>
+        <v>4.819656734745779</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.539730250134927</v>
+        <v>4.819656795370582</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.53973012130722</v>
+        <v>4.819656666542874</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.539730257713027</v>
+        <v>4.819656802948683</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.539730432009336</v>
+        <v>4.819656977244991</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.539730575993244</v>
+        <v>4.819657121228899</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.539730409275035</v>
+        <v>4.819656954510689</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.539730401696935</v>
+        <v>4.819656946932589</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.53973011372912</v>
+        <v>4.819656658964774</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.539730128885321</v>
+        <v>4.819656674120976</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.539730356228333</v>
+        <v>4.819656901463987</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.539730341072132</v>
+        <v>4.819656886307786</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.539730447165537</v>
+        <v>4.819656992401192</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.539730174353923</v>
+        <v>4.819656719589578</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.539730272869229</v>
+        <v>4.819656818104883</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.539730424431236</v>
+        <v>4.819656969666891</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.539730439587437</v>
+        <v>4.819656984823092</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.539730416853136</v>
+        <v>4.819656962088791</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.53973050021224</v>
+        <v>4.819657045447895</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.539730598727545</v>
+        <v>4.8196571439632</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.539730432009336</v>
+        <v>4.819656977244991</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.539730416853136</v>
+        <v>4.819656962088791</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.539730386540734</v>
+        <v>4.819656931776389</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.539730371384533</v>
+        <v>4.819656916620189</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.539730409275035</v>
+        <v>4.819656954510689</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.539730424431236</v>
+        <v>4.819656969666891</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.539730416853136</v>
+        <v>4.819656962088791</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006876111030578613</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.006984848529100418</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007093355059623718</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0002237223088741302</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.004531353712081909</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.006252836436033249</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1382051466884343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.007327698171138763</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1382051466884343</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.006835665553808212</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.007212106138467789</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.007008031010627747</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.007529016584157944</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.007908836007118225</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.007075577974319458</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.006894517689943314</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.006211109459400177</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.007496856153011322</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.007662326097488403</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.007931482046842575</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.007290024310350418</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.007464312016963959</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.006155788898468018</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.003683052957057953</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.004918675869703293</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.005753029137849808</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.006080180406570435</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.006289757788181305</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.006715048104524612</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.005510233342647552</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.00506163015961647</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.005656048655509949</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.005860019475221634</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.005806472152471542</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.005857441574335098</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.005658660084009171</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.003220900893211365</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.003759879618883133</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.980598284437189</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0001044422388076782</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.980598284437189</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0001506991684436798</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001702487156966236</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.962716250749892</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0003814958035945892</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1382051466884343</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>3.928466506614503</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2943180570367409</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0009135007858276367</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.551752134757981</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.3679933361985089</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.001800950616598129</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7211965688743771</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.993467489878253</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.5275167022683547</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.00157831609249115</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.980598284437189</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>3.680715233143757</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.5643380329722558</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.003064345568418503</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>4.281914624169513</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5980853050984786</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.004310347139835358</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>4.913789208780242</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2699047745371187</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.003245484083890915</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.980598284437189</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>4.855016446243654</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1303510265252164</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001943532377481461</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.980598284437189</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>4.845603369834006</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.06210838334216721</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.001642867922782898</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>4.839365532581605</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01840228074926474</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.002392683178186417</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7211965688743771</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>4.813995053420325</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01217112964989038</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-6.874650716781616e-05</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>4.819926951140156</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.006227371713833546</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.002381768077611923</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>4.820202361553724</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003183098989336598</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0005868487060070038</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>4.820337480361069</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001193148823900667</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001292712986469269</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>4.819539021041916</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006484047339888131</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.001890957355499268</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>4.819641256924198</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000309713060421098</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.002332661300897598</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>4.819611865148119</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.000189823113252138</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0016285739839077</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>4.819681651151106</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>9.690754659105971e-05</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.00372784212231636</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>4.819685529937242</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>4.395556340847371e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.006794292479753494</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>4.819677469419536</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.697865944406779e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0002773702144622803</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>4.81968645009054</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.987335331640211e-06</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001691542565822601</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1382051466884343</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>4.819678591308692</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.002810008823871613</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1382051466884343</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>4.819671810518222</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001984108239412308</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>4.819667389974372</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001677423715591431</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>4.819661811679247</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0001314282417297363</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7211965688743771</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>4.819656765058181</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.004396356642246246</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>4.819657083338397</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0001222416758537292</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>4.819658174584854</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.00739772617816925</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1382051466884343</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC67" t="n">
-        <v>4.819657484977718</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002720650285482407</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>4.819657515290119</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.004612021148204803</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>4.81965732583761</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002383887767791748</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>4.819657378884313</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003098126500844955</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>4.819657431931015</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003277953714132309</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>4.819657394040513</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.002486847341060638</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>4.819657265212806</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002380598336458206</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>4.819657121228899</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002655047923326492</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>4.819656962088791</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.002527389675378799</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>4.819657015135493</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004005704075098038</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>4.819656962088791</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002668146044015884</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>4.819656962088791</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.002145953476428986</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>4.819656780214381</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001441057771444321</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>4.819656946932589</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002767860889434814</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>4.8196571439632</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003945443779230118</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>4.819656984823092</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002223357558250427</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>4.819657022713593</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.001111447811126709</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>4.819657219744204</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002655953168869019</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>4.819657197009902</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.003644328564405441</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>4.819657045447895</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003634471446275711</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>4.819656969666891</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.003194741904735565</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>4.819657068182196</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001487258821725845</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>4.819657075760296</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.002283245325088501</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>4.81965734099381</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.003306776285171509</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>4.819657045447895</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.002067722380161285</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>4.819657287947107</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.00338432565331459</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>4.819657371306212</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0007144622504711151</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>4.819657204588004</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002386689186096191</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>4.819657394040513</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.002632375806570053</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1382051466884343</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>4.819657045447895</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003933515399694443</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1382051466884343</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>4.819656840839184</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.00402272492647171</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>4.819656954510689</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002872727811336517</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>4.819656969666891</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.003333251923322678</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>4.819656734745779</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003870703279972076</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>4.819656795370582</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004429496824741364</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>4.819656666542874</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00116337463259697</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>4.819656802948683</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003625359386205673</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>4.819656977244991</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003652032464742661</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>4.819657121228899</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003522589802742004</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>4.819656954510689</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003158215433359146</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>4.819656946932589</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004318613559007645</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>4.819656658964774</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004380736500024796</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>4.819656674120976</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004212614148855209</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>4.819656901463987</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003520265221595764</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>4.819656886307786</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004295859485864639</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>4.819656992401192</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004532445222139359</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>4.819656719589578</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004272624850273132</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>4.819656818104883</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.00413169339299202</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>4.819656969666891</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00425112247467041</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>4.819656984823092</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.004004202783107758</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>4.819656962088791</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003674969077110291</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>4.819657045447895</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.004464838653802872</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>4.8196571439632</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004441231489181519</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>4.819656977244991</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.004355289041996002</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>4.819656962088791</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004089221358299255</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>4.819656931776389</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004092462360858917</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>4.819656916620189</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004328429698944092</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>4.819656954510689</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00384819507598877</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3700000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>4.819656969666891</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003197979182004929</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>4.819656962088791</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_2_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_2_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.006876111030578613</v>
+        <v>-0.006876096129417419</v>
       </c>
       <c r="JB2" t="n">
         <v>-1</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.006984848529100418</v>
+        <v>-0.00698481872677803</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.007093355059623718</v>
+        <v>-0.007093340158462524</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.0002237223088741302</v>
+        <v>0.0002237372100353241</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.004531353712081909</v>
+        <v>-0.004531368613243103</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.006252836436033249</v>
+        <v>-0.006252851337194443</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.007327698171138763</v>
+        <v>-0.007327686995267868</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.006835665553808212</v>
+        <v>-0.006835661828517914</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.007212106138467789</v>
+        <v>-0.00721210241317749</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.007008031010627747</v>
+        <v>-0.007008038461208344</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.007529016584157944</v>
+        <v>-0.00752900168299675</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.007908836007118225</v>
+        <v>-0.007908839732408524</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.007075577974319458</v>
+        <v>-0.00707557424902916</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.006894517689943314</v>
+        <v>-0.006894525140523911</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.1199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.006211109459400177</v>
+        <v>-0.006211098283529282</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.007496856153011322</v>
+        <v>-0.007496874779462814</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.007662326097488403</v>
+        <v>-0.007662333548069</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.1199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.007931482046842575</v>
+        <v>-0.007931485772132874</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.007290024310350418</v>
+        <v>-0.00729004293680191</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.1199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.007464312016963959</v>
+        <v>-0.007464297115802765</v>
       </c>
       <c r="JB21" t="n">
         <v>0.16</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.006155788898468018</v>
+        <v>-0.006155773997306824</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.003683052957057953</v>
+        <v>-0.003683049231767654</v>
       </c>
       <c r="JB23" t="n">
         <v>0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.004918675869703293</v>
+        <v>-0.004918694496154785</v>
       </c>
       <c r="JB24" t="n">
         <v>0.9999999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.005753029137849808</v>
+        <v>-0.005753036588430405</v>
       </c>
       <c r="JB25" t="n">
         <v>0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.006080180406570435</v>
+        <v>-0.006080184131860733</v>
       </c>
       <c r="JB26" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.006715048104524612</v>
+        <v>-0.006715092808008194</v>
       </c>
       <c r="JB28" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.005510233342647552</v>
+        <v>-0.005510229617357254</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.005656048655509949</v>
+        <v>-0.005656011402606964</v>
       </c>
       <c r="JB31" t="n">
         <v>0.2599999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.005860019475221634</v>
+        <v>-0.005860026925802231</v>
       </c>
       <c r="JB32" t="n">
         <v>0.8599999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.005806472152471542</v>
+        <v>-0.005806475877761841</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.005857441574335098</v>
+        <v>-0.005857449024915695</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.005658660084009171</v>
+        <v>-0.005658645182847977</v>
       </c>
       <c r="JB35" t="n">
         <v>0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.003220900893211365</v>
+        <v>-0.003220867365598679</v>
       </c>
       <c r="JB36" t="n">
         <v>0.7199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.003759879618883133</v>
+        <v>0.003759849816560745</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0001044422388076782</v>
+        <v>0.0001044273376464844</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0001506991684436798</v>
+        <v>-0.0001507215201854706</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0003814958035945892</v>
+        <v>-0.0003815069794654846</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0009135007858276367</v>
+        <v>-0.0009134821593761444</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.001800950616598129</v>
+        <v>-0.001800946891307831</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.00157831609249115</v>
+        <v>0.001578304916620255</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.003064345568418503</v>
+        <v>0.003064312040805817</v>
       </c>
       <c r="JB44" t="n">
         <v>0.2599999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.004310347139835358</v>
+        <v>0.004310350865125656</v>
       </c>
       <c r="JB45" t="n">
         <v>0.2599999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.003245484083890915</v>
+        <v>0.003245487809181213</v>
       </c>
       <c r="JB46" t="n">
         <v>0.2599999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001943532377481461</v>
+        <v>-0.001943513751029968</v>
       </c>
       <c r="JB47" t="n">
         <v>0.1199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.001642867922782898</v>
+        <v>0.001642905175685883</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.02000000000000007</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.002392683178186417</v>
+        <v>-0.002392716705799103</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.16</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-6.874650716781616e-05</v>
+        <v>-6.873160600662231e-05</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.002381768077611923</v>
+        <v>-0.002381779253482819</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.16</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0005868487060070038</v>
+        <v>-0.000586826354265213</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.02000000000000007</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.001292712986469269</v>
+        <v>-0.001292690634727478</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.16</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.001890957355499268</v>
+        <v>-0.001890964806079865</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.002332661300897598</v>
+        <v>-0.002332683652639389</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.3</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0016285739839077</v>
+        <v>-0.001628555357456207</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.16</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.00372784212231636</v>
+        <v>-0.003727857023477554</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.1600000000000001</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.006794292479753494</v>
+        <v>0.00679425522685051</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.16</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.0002773702144622803</v>
+        <v>-0.0002773851156234741</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.001691542565822601</v>
+        <v>-0.001691509038209915</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.4399999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.002810008823871613</v>
+        <v>-0.002810042351484299</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.7199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.001984108239412308</v>
+        <v>-0.001984152942895889</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001677423715591431</v>
+        <v>-0.001677412539720535</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0001314282417297363</v>
+        <v>-0.0001314468681812286</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.004396356642246246</v>
+        <v>0.004396364092826843</v>
       </c>
       <c r="JB65" t="n">
         <v>0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0001222416758537292</v>
+        <v>-0.0001222044229507446</v>
       </c>
       <c r="JB66" t="n">
         <v>0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.00739772617816925</v>
+        <v>-0.007397715002298355</v>
       </c>
       <c r="JB67" t="n">
         <v>0.02000000000000007</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.002720650285482407</v>
+        <v>-0.0027206651866436</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.8599999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.004612021148204803</v>
+        <v>-0.004612009972333908</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.002383887767791748</v>
+        <v>-0.002383895218372345</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.003098126500844955</v>
+        <v>-0.003098122775554657</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.003277953714132309</v>
+        <v>-0.003277957439422607</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.002486847341060638</v>
+        <v>-0.002486832439899445</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.002380598336458206</v>
+        <v>-0.002380561083555222</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002655047923326492</v>
+        <v>-0.002655033022165298</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.002527389675378799</v>
+        <v>-0.002527393400669098</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.004005704075098038</v>
+        <v>-0.004005689173936844</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002668146044015884</v>
+        <v>-0.002668142318725586</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.1199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.002145953476428986</v>
+        <v>-0.002145964652299881</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.1199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001441057771444321</v>
+        <v>-0.001441061496734619</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002767860889434814</v>
+        <v>-0.002767875790596008</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.1199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.003945443779230118</v>
+        <v>-0.003945440053939819</v>
       </c>
       <c r="JB82" t="n">
         <v>0.16</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002223357558250427</v>
+        <v>-0.00222339853644371</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.001111447811126709</v>
+        <v>-0.001111432909965515</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.1199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.003644328564405441</v>
+        <v>-0.003644309937953949</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.003634471446275711</v>
+        <v>-0.003634504973888397</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.8599999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.002283245325088501</v>
+        <v>-0.002283304929733276</v>
       </c>
       <c r="JB90" t="n">
         <v>0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.002067722380161285</v>
+        <v>-0.002067726105451584</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.00338432565331459</v>
+        <v>-0.003384340554475784</v>
       </c>
       <c r="JB93" t="n">
         <v>0.3</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.0007144622504711151</v>
+        <v>0.000714477151632309</v>
       </c>
       <c r="JB94" t="n">
         <v>0.5799999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.002386689186096191</v>
+        <v>-0.002386707812547684</v>
       </c>
       <c r="JB95" t="n">
         <v>0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.002632375806570053</v>
+        <v>-0.002632368355989456</v>
       </c>
       <c r="JB96" t="n">
         <v>0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.003933515399694443</v>
+        <v>-0.003933493047952652</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.5799999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.00402272492647171</v>
+        <v>-0.004022695124149323</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.002872727811336517</v>
+        <v>-0.00287274643778801</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.003333251923322678</v>
+        <v>-0.003333292901515961</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.003870703279972076</v>
+        <v>-0.003870699554681778</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.004429496824741364</v>
+        <v>-0.004429526627063751</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.00116337463259697</v>
+        <v>-0.001163370907306671</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.003625359386205673</v>
+        <v>-0.00362536683678627</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003652032464742661</v>
+        <v>-0.003652028739452362</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.003158215433359146</v>
+        <v>-0.003158207982778549</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.004318613559007645</v>
+        <v>-0.004318628460168839</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004380736500024796</v>
+        <v>-0.004380732774734497</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.004212614148855209</v>
+        <v>-0.004212606698274612</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003520265221595764</v>
+        <v>-0.003520231693983078</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.004532445222139359</v>
+        <v>-0.004532448947429657</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.004272624850273132</v>
+        <v>-0.004272650927305222</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.00413169339299202</v>
+        <v>-0.004131712019443512</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.00425112247467041</v>
+        <v>-0.004251126199960709</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.004004202783107758</v>
+        <v>-0.004004240036010742</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003674969077110291</v>
+        <v>-0.003674950450658798</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.004464838653802872</v>
+        <v>-0.004464812576770782</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.004441231489181519</v>
+        <v>-0.004441224038600922</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.004355289041996002</v>
+        <v>-0.004355285316705704</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.004089221358299255</v>
+        <v>-0.004089202731847763</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.004092462360858917</v>
+        <v>-0.004092466086149216</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.2599999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.004328429698944092</v>
+        <v>-0.004328425973653793</v>
       </c>
       <c r="JB124" t="n">
         <v>0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.00384819507598877</v>
+        <v>-0.003848202526569366</v>
       </c>
       <c r="JB125" t="n">
         <v>0.3700000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.003197979182004929</v>
+        <v>-0.00319797545671463</v>
       </c>
       <c r="JB126" t="n">
         <v>0.7200000000000004</v>
